--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-005_申請作成_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-005_申請作成_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="14678025"/>
+    <ext cx="8572500" cy="14878050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-005 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-005 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>申請者 userId は JWT の sub（Long.valueOf(jwt.getSubject())）のみから決める。リクエスト本文に userId が含まれていても DTO に項目が無いため無視する（他人名義での申請を不可能にする）。ロールによる制限はなく、EMPLOYEE / MANAGER / ADMIN の全員が自分の申請を作成できる（KF-BD-004）。</t>
+          <t>申請者 userId は JWT の sub（Long.valueOf(auth.getName())）のみから決める。リクエスト本文に userId が含まれていても DTO に項目が無いため無視する（他人名義での申請を不可能にする）。ロールによる制限はなく、EMPLOYEE / MANAGER / ADMIN の全員が自分の申請を作成できる（KF-BD-004）。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>PENDING で登録。days=3.0、current_step=1、submitted_at=now(JST)、steps 2行（1段目=上長 WAITING、2段目=approver null）</t>
+          <t>PENDING で登録。days=3.0、current_step=1、submitted_at=now(clock)、steps 2行（1段目=上長 WAITING、2段目=approver null）</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="94" customHeight="1">
+    <row r="3" ht="229" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2299,7 +2299,11 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：NotificationService#notify を完全定義（type / request_id 保存）、Notification Entity・NotificationType 追加、updated_at をトリガ方式に統一、getHolidayDates / findByHolidayDateBetweenOrderByHolidayDate に命名統一、E-004 を常に 409、tables の U 追記、提出共通処理（checkSubmittable / startApproval）の切り出し（ONL-022 と共用）</t>
+          <t>・確定設計変更 D1〜D10 を反映：NotificationService#notify を完全定義（type / request_id 保存）、Notification Entity・NotificationType 追加、updated_at をトリガ方式に統一、getHolidayDates / findByHolidayDateBetweenOrderByHolidayDate に命名統一、E-004 を常に 409、tables の U 追記、提出共通処理（checkSubmittable / startApproval）の切り出し（ONL-022 と共用）
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・Controller は Authentication#getName() でユーザーIDを取得、時刻は Clock Bean 注入に統一（コードを正とする）
+・RequestStatus の ALL / WITHDRAWABLE / SUBMITTABLE は RequestService 内の private 定数として実装
+・LeaveType の有効判定は Boolean.TRUE.equals(getIsActive()) とし null 安全にした</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -4758,7 +4762,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public CreateRequestResponse create(@AuthenticationPrincipal Jwt jwt, @Valid @RequestBody CreateRequestRequest request)</t>
+          <t>public CreateRequestResponse create(Authentication auth, @Valid @RequestBody CreateRequestRequest request)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4822,17 +4826,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン（sub = users.id）。@AuthenticationPrincipal で注入</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -4903,7 +4907,7 @@
         <is>
           <t>1. 本文を CreateRequestRequest に変換する（失敗 → HttpMessageNotReadableException）
 2. @Valid により制約を検証する（失敗 → MethodArgumentNotValidException）
-3. Long userId = Long.valueOf(jwt.getSubject());   // 申請者は常にトークンから取得。本文の値は使わない
+3. Long userId = Long.valueOf(auth.getName());   // 申請者は常にトークンから取得。本文の値は使わない
 4. return requestService.create(userId, request);</t>
         </is>
       </c>
@@ -5122,8 +5126,8 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>today = LocalDate.now(JST);
-now   = LocalDateTime.now(JST).truncatedTo(ChronoUnit.SECONDS);   // DB は JST の日時で保存
+          <t>today = LocalDate.now(clock);
+now   = LocalDateTime.now(clock).truncatedTo(ChronoUnit.SECONDS);   // DB は JST の日時で保存
 draft = Boolean.TRUE.equals(req.asDraft());
 leave = RequestType.LEAVE.equals(req.requestType());
 validateInput(req, today, draft);                                    // ② E-002 / E-003
